--- a/tasks/finalpool/yf-financial-health-excel-notion/groundtruth_workspace/Financial_Health_Report.xlsx
+++ b/tasks/finalpool/yf-financial-health-excel-notion/groundtruth_workspace/Financial_Health_Report.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>637959000000</v>
+        <v>716924000000</v>
       </c>
       <c r="C2" t="n">
-        <v>59248000000</v>
+        <v>77670000000</v>
       </c>
       <c r="D2" t="n">
-        <v>9.300000000000001</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="3">
@@ -462,13 +462,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>350018000000</v>
+        <v>402836000000</v>
       </c>
       <c r="C3" t="n">
-        <v>100118000000</v>
+        <v>132170000000</v>
       </c>
       <c r="D3" t="n">
-        <v>28.6</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88821000000</v>
+        <v>94193000000</v>
       </c>
       <c r="C4" t="n">
-        <v>14066000000</v>
+        <v>26804000000</v>
       </c>
       <c r="D4" t="n">
-        <v>15.8</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="5">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>169439000000</v>
+        <v>181847000000</v>
       </c>
       <c r="C5" t="n">
-        <v>58471000000</v>
+        <v>57048000000</v>
       </c>
       <c r="D5" t="n">
-        <v>34.5</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>339247000000</v>
+        <v>323905000000</v>
       </c>
       <c r="C6" t="n">
-        <v>33680000000</v>
+        <v>28844000000</v>
       </c>
       <c r="D6" t="n">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>624894000000</v>
+        <v>818042000000</v>
       </c>
       <c r="C2" t="n">
-        <v>338924000000</v>
+        <v>406977000000</v>
       </c>
       <c r="D2" t="n">
-        <v>285970000000</v>
+        <v>411065000000</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>450256000000</v>
+        <v>595281000000</v>
       </c>
       <c r="C3" t="n">
-        <v>125172000000</v>
+        <v>180016000000</v>
       </c>
       <c r="D3" t="n">
-        <v>325084000000</v>
+        <v>415265000000</v>
       </c>
     </row>
     <row r="4">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>180104000000</v>
+        <v>199210000000</v>
       </c>
       <c r="C4" t="n">
-        <v>108614000000</v>
+        <v>117666000000</v>
       </c>
       <c r="D4" t="n">
-        <v>71490000000</v>
+        <v>81544000000</v>
       </c>
     </row>
     <row r="5">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4002814000000</v>
+        <v>4424900000000</v>
       </c>
       <c r="C5" t="n">
-        <v>3658056000000</v>
+        <v>4062462000000</v>
       </c>
       <c r="D5" t="n">
-        <v>344758000000</v>
+        <v>362438000000</v>
       </c>
     </row>
     <row r="6">
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>453475000000</v>
+        <v>448980000000</v>
       </c>
       <c r="C6" t="n">
-        <v>182869000000</v>
+        <v>182354000000</v>
       </c>
       <c r="D6" t="n">
-        <v>270606000000</v>
+        <v>259386000000</v>
       </c>
     </row>
   </sheetData>
